--- a/src/test/resources/ITSM Test Data/ITSM_Test_Data.xlsx
+++ b/src/test/resources/ITSM Test Data/ITSM_Test_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Excel Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A0DF23-78CD-4398-9984-1622B3912D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D9030C-5C8F-4148-A95A-8B97AD5AD7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C05C510-62EF-4AE2-93E3-C18FC0E5A82A}"/>
   </bookViews>
@@ -55,8 +55,7 @@
     <t>U5m0$PWk=vU</t>
   </si>
   <si>
-    <t xml:space="preserve">63JIezx/Qk+B
-</t>
+    <t>fH-llx7U8=UQ</t>
   </si>
 </sst>
 </file>
@@ -464,7 +463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" s="2" customFormat="1" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
